--- a/verification/cases/roundtrip/formulas_math_basic/init.xlsx
+++ b/verification/cases/roundtrip/formulas_math_basic/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/math-basic/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3178D93C-C0B3-E042-9881-9EEC8DDEA4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B297B01-0EC7-4B56-B377-3232262FE108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{624D7C72-09A9-1B41-8369-5D9A99CA846B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{624D7C72-09A9-1B41-8369-5D9A99CA846B}"/>
   </bookViews>
   <sheets>
     <sheet name="Math Tests" sheetId="1" r:id="rId1"/>
@@ -672,7 +672,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -695,13 +695,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C56AAEC-1253-9C49-A6E3-6A6B13E494D3}">
   <dimension ref="B2:K1176"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -715,7 +715,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -727,7 +727,7 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -741,7 +741,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
         <v>2</v>
       </c>
@@ -757,7 +757,7 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>3</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
         <v>4</v>
       </c>
@@ -789,7 +789,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="15" t="s">
         <v>5</v>
       </c>
@@ -805,7 +805,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
         <v>6</v>
       </c>
@@ -821,7 +821,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="15" t="s">
         <v>9</v>
       </c>
@@ -838,7 +838,7 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
         <v>10</v>
       </c>
@@ -855,7 +855,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="15" t="s">
         <v>7</v>
       </c>
@@ -872,7 +872,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="15" t="s">
         <v>8</v>
       </c>
@@ -889,7 +889,7 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -901,7 +901,7 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -913,7 +913,7 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
@@ -927,7 +927,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>12</v>
       </c>
@@ -959,7 +959,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="12">
         <v>0</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="12">
         <v>1</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="12">
         <v>-1</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="12">
         <v>42.5</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="12">
         <v>-42.5</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1340,7 +1340,7 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1352,7 +1352,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
         <v>13</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>12</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="12">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="12">
         <v>1</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="12">
         <v>-1</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="12">
         <v>42.5</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="12">
         <v>-42.5</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -1779,7 +1779,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -1791,7 +1791,7 @@
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="6" t="s">
         <v>14</v>
       </c>
@@ -1805,7 +1805,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
         <v>12</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="12">
         <v>0</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="12">
         <v>1</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="12">
         <v>-1</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="12">
         <v>42.5</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="12">
         <v>-42.5</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>-9.9999999999999911</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>9.9999999999999858</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -2218,7 +2218,7 @@
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -2230,7 +2230,7 @@
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
-    <row r="55" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="6" t="s">
         <v>15</v>
       </c>
@@ -2244,7 +2244,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="12">
         <v>0</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="12">
         <v>1</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="12">
         <v>-1</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="12">
         <v>42.5</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>-4.2500000000000045E-307</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="12">
         <v>-42.5</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>4.2500000000000045E-307</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -2657,7 +2657,7 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -2669,7 +2669,7 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
     </row>
-    <row r="68" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="6" t="s">
         <v>16</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
         <v>12</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="12">
         <v>0</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="12">
         <v>1</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="12">
         <v>-1</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="12">
         <v>42.5</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="12">
         <v>-42.5</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
@@ -3096,7 +3096,7 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -3108,7 +3108,7 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
     </row>
-    <row r="81" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="6" t="s">
         <v>17</v>
       </c>
@@ -3122,7 +3122,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
         <v>12</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="12">
         <v>0</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="12">
         <v>1</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="12">
         <v>-1</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="12">
         <v>42.5</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="12">
         <v>-42.5</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>-42.5</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>-9.9999999999999951E-308</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
@@ -3535,7 +3535,7 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
@@ -3547,7 +3547,7 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
     </row>
-    <row r="94" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="6" t="s">
         <v>18</v>
       </c>
@@ -3561,7 +3561,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
         <v>12</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" s="12">
         <v>0</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B97" s="12">
         <v>1</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B98" s="12">
         <v>-1</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="12">
         <v>42.5</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" s="12">
         <v>-42.5</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
@@ -3974,7 +3974,7 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
@@ -3986,7 +3986,7 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
     </row>
-    <row r="107" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B107" s="5" t="s">
         <v>19</v>
       </c>
@@ -4000,7 +4000,7 @@
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -4012,7 +4012,7 @@
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" s="10" t="s">
         <v>20</v>
       </c>
@@ -4026,7 +4026,7 @@
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" s="12">
         <v>0</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="12">
         <v>1</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" s="12">
         <v>-1</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B113" s="12">
         <v>42.5</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>1.4050061177528801E+51</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B114" s="12">
         <v>-42.5</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
@@ -4407,7 +4407,7 @@
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
@@ -4419,7 +4419,7 @@
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
     </row>
-    <row r="121" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B121" s="5" t="s">
         <v>30</v>
       </c>
@@ -4433,7 +4433,7 @@
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
@@ -4445,7 +4445,7 @@
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
     </row>
-    <row r="123" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B123" s="6" t="s">
         <v>31</v>
       </c>
@@ -4459,7 +4459,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B124" s="7" t="s">
         <v>32</v>
       </c>
@@ -4473,7 +4473,7 @@
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B125" s="12">
         <v>0</v>
       </c>
@@ -4502,7 +4502,7 @@
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B126" s="12">
         <v>1</v>
       </c>
@@ -4531,7 +4531,7 @@
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B127" s="12">
         <v>-1</v>
       </c>
@@ -4560,7 +4560,7 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B128" s="12">
         <v>42.5</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B129" s="12">
         <v>-42.5</v>
       </c>
@@ -4618,7 +4618,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B130" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -4647,7 +4647,7 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B131" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -4676,7 +4676,7 @@
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B132" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -4705,7 +4705,7 @@
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B133" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -4734,7 +4734,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
@@ -4746,7 +4746,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
@@ -4758,7 +4758,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
     </row>
-    <row r="136" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B136" s="6" t="s">
         <v>33</v>
       </c>
@@ -4772,7 +4772,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B137" s="7" t="s">
         <v>32</v>
       </c>
@@ -4786,7 +4786,7 @@
       <c r="J137" s="11"/>
       <c r="K137" s="11"/>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B138" s="12">
         <v>0</v>
       </c>
@@ -4815,7 +4815,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B139" s="12">
         <v>1</v>
       </c>
@@ -4844,7 +4844,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B140" s="12">
         <v>-1</v>
       </c>
@@ -4873,7 +4873,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B141" s="12">
         <v>42.5</v>
       </c>
@@ -4902,7 +4902,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B142" s="12">
         <v>-42.5</v>
       </c>
@@ -4931,7 +4931,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B143" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B144" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -4989,7 +4989,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B145" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -5018,7 +5018,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -5047,7 +5047,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
@@ -5059,7 +5059,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
@@ -5071,7 +5071,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
     </row>
-    <row r="149" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B149" s="6" t="s">
         <v>34</v>
       </c>
@@ -5085,7 +5085,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B150" s="7" t="s">
         <v>32</v>
       </c>
@@ -5099,7 +5099,7 @@
       <c r="J150" s="11"/>
       <c r="K150" s="11"/>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B151" s="12">
         <v>0</v>
       </c>
@@ -5128,7 +5128,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B152" s="12">
         <v>1</v>
       </c>
@@ -5157,7 +5157,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B153" s="12">
         <v>-1</v>
       </c>
@@ -5186,7 +5186,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="12">
         <v>42.5</v>
       </c>
@@ -5215,7 +5215,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B155" s="12">
         <v>-42.5</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B156" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -5302,7 +5302,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B158" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -5331,7 +5331,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B159" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -5360,7 +5360,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
@@ -5372,7 +5372,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
@@ -5384,7 +5384,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
     </row>
-    <row r="162" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B162" s="6" t="s">
         <v>35</v>
       </c>
@@ -5398,7 +5398,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B163" s="7" t="s">
         <v>36</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="J163" s="11"/>
       <c r="K163" s="11"/>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B164" s="12">
         <v>0</v>
       </c>
@@ -5441,7 +5441,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B165" s="12">
         <v>1</v>
       </c>
@@ -5470,7 +5470,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B166" s="12">
         <v>-1</v>
       </c>
@@ -5499,7 +5499,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B167" s="12">
         <v>42.5</v>
       </c>
@@ -5528,7 +5528,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B168" s="12">
         <v>-42.5</v>
       </c>
@@ -5557,7 +5557,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B169" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -5586,7 +5586,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B170" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -5615,7 +5615,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B171" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -5644,7 +5644,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B172" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -5673,7 +5673,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
@@ -5685,7 +5685,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
@@ -5697,7 +5697,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
     </row>
-    <row r="175" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B175" s="6" t="s">
         <v>37</v>
       </c>
@@ -5711,7 +5711,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B176" s="7" t="s">
         <v>36</v>
       </c>
@@ -5725,7 +5725,7 @@
       <c r="J176" s="11"/>
       <c r="K176" s="11"/>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B177" s="12">
         <v>0</v>
       </c>
@@ -5754,7 +5754,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B178" s="12">
         <v>1</v>
       </c>
@@ -5783,7 +5783,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B179" s="12">
         <v>-1</v>
       </c>
@@ -5812,7 +5812,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B180" s="12">
         <v>42.5</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B181" s="12">
         <v>-42.5</v>
       </c>
@@ -5870,7 +5870,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B182" s="13">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -5899,7 +5899,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B183" s="13">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -5928,7 +5928,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B184" s="13">
         <v>9.990000000000001E+307</v>
       </c>
@@ -5957,7 +5957,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B185" s="13">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -5986,7 +5986,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
@@ -5998,7 +5998,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
@@ -6010,7 +6010,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
@@ -6022,12 +6022,12 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
     </row>
-    <row r="190" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B190" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B191" s="17" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B192" s="17" t="e">
         <v>#NUM!</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B193" s="17" t="e">
         <v>#VALUE!</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B194" s="17" t="s">
         <v>42</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="1109" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="1109" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C1109" s="2" t="s">
         <v>21</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="1124" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1124" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1124" s="2">
         <v>-2</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1137" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1137" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1137" s="2">
         <v>-2</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1150" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1150" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1150" s="2">
         <v>-2</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1163" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1163" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1163" s="2">
         <v>1</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="1176" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1176" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1176" s="2">
         <v>1</v>
       </c>
